--- a/tools/importer/reports/import-articles.report.xlsx
+++ b/tools/importer/reports/import-articles.report.xlsx
@@ -52,7 +52,7 @@
     <t>articles</t>
   </si>
   <si>
-    <t>2026-09-30T23:31:55.698Z</t>
+    <t>2026-09-30T23:48:39.575Z</t>
   </si>
   <si>
     <t>Why technology supply chains remain under pressure</t>
